--- a/dev/StructureDefinition-ph-core-medication.xlsx
+++ b/dev/StructureDefinition-ph-core-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T05:11:07+00:00</t>
+    <t>2026-03-16T07:24:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-medication.xlsx
+++ b/dev/StructureDefinition-ph-core-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T07:24:26+00:00</t>
+    <t>2026-03-16T20:48:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-medication.xlsx
+++ b/dev/StructureDefinition-ph-core-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T20:48:05+00:00</t>
+    <t>2026-03-16T20:59:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-medication.xlsx
+++ b/dev/StructureDefinition-ph-core-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T20:59:47+00:00</t>
+    <t>2026-03-16T21:16:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-medication.xlsx
+++ b/dev/StructureDefinition-ph-core-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T21:16:15+00:00</t>
+    <t>2026-03-16T21:44:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-medication.xlsx
+++ b/dev/StructureDefinition-ph-core-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T21:44:19+00:00</t>
+    <t>2026-03-16T21:58:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-medication.xlsx
+++ b/dev/StructureDefinition-ph-core-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T21:58:37+00:00</t>
+    <t>2026-03-16T22:06:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-medication.xlsx
+++ b/dev/StructureDefinition-ph-core-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T22:06:54+00:00</t>
+    <t>2026-03-16T22:26:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-medication.xlsx
+++ b/dev/StructureDefinition-ph-core-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T22:26:22+00:00</t>
+    <t>2026-03-19T20:53:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-medication.xlsx
+++ b/dev/StructureDefinition-ph-core-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T20:53:49+00:00</t>
+    <t>2026-03-19T21:27:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-medication.xlsx
+++ b/dev/StructureDefinition-ph-core-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T21:27:42+00:00</t>
+    <t>2026-04-08T04:20:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-medication.xlsx
+++ b/dev/StructureDefinition-ph-core-medication.xlsx
@@ -9,11 +9,14 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$42</definedName>
+  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1078" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1549" uniqueCount="285">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T04:20:57+00:00</t>
+    <t>2026-04-10T05:32:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -509,9 +512,6 @@
     <t>Depending on the context of use, the code that was actually selected by the user (prescriber, dispenser, etc.) will have the coding.userSelected set to true.  As described in the coding datatype: "A coding may be marked as a "userSelected" if a user selected the particular coded value in a user interface (e.g. the user selects an item in a pick-list). If a user selected coding exists, it is the preferred choice for performing translations etc. Other codes can only be literal translations to alternative code systems, or codes at a lower level of granularity (e.g. a generic code for a vendor-specific primary one).</t>
   </si>
   <si>
-    <t>extensible</t>
-  </si>
-  <si>
     <t>http://doh.gov.ph/fhir/ph-core/ValueSet/drugs-vs</t>
   </si>
   <si>
@@ -531,6 +531,96 @@
     <t>RXO-1.1-Requested Give Code.code / RXE-2.1-Give Code.code / RXD-2.1-Dispense/Give Code.code / RXG-4.1-Give Code.code /RXA-5.1-Administered Code.code / RXC-2.1 Component Code</t>
   </si>
   <si>
+    <t>Medication.code.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Medication.code.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Medication.code.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>Medication.code.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
     <t>Medication.status</t>
   </si>
   <si>
@@ -612,6 +702,18 @@
     <t>RXO-5-Requested Dosage Form / RXE-6-Give Dosage Form / RXD-6-Actual Dosage Form / RXG-8-Give Dosage Form / RXA-8-Administered Dosage Form</t>
   </si>
   <si>
+    <t>Medication.form.id</t>
+  </si>
+  <si>
+    <t>Medication.form.extension</t>
+  </si>
+  <si>
+    <t>Medication.form.coding</t>
+  </si>
+  <si>
+    <t>Medication.form.text</t>
+  </si>
+  <si>
     <t>Medication.amount</t>
   </si>
   <si>
@@ -650,29 +752,7 @@
     <t>Medication.ingredient.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Medication.ingredient.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>Medication.ingredient.modifierExtension</t>
@@ -708,10 +788,44 @@
     <t>The ingredient may reference a substance (for example, amoxicillin) or another medication (for example in the case of a compounded product, Glaxal Base).</t>
   </si>
   <si>
+    <t xml:space="preserve">type:$this}
+</t>
+  </si>
+  <si>
     <t>.player</t>
   </si>
   <si>
     <t>RXC-2-Component Code  if medication: RXO-1-Requested Give Code / RXE-2-Give Code / RXD-2-Dispense/Give Code / RXG-4-Give Code / RXA-5-Administered Code</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x]:itemCodeableConcept</t>
+  </si>
+  <si>
+    <t>itemCodeableConcept</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x]:itemCodeableConcept.id</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].id</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x]:itemCodeableConcept.extension</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].extension</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x]:itemCodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x]:itemCodeableConcept.text</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].text</t>
   </si>
   <si>
     <t>Medication.ingredient.isActive</t>
@@ -927,6 +1041,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -1102,12 +1231,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN29"/>
+  <dimension ref="A1:AN42"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="32.79296875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="50.4140625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="32.79296875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="18.3359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -1133,7 +1262,7 @@
     <col min="26" max="26" width="45.22265625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
@@ -1268,7 +1397,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
         <v>31</v>
       </c>
@@ -1380,7 +1509,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
         <v>87</v>
       </c>
@@ -1494,7 +1623,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
         <v>95</v>
       </c>
@@ -1606,7 +1735,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
         <v>101</v>
       </c>
@@ -1720,7 +1849,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
         <v>107</v>
       </c>
@@ -1834,7 +1963,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
         <v>116</v>
       </c>
@@ -1948,7 +2077,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
         <v>124</v>
       </c>
@@ -2062,7 +2191,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
         <v>132</v>
       </c>
@@ -2176,7 +2305,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
         <v>140</v>
       </c>
@@ -2292,7 +2421,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
         <v>145</v>
       </c>
@@ -2425,7 +2554,7 @@
         <v>88</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>78</v>
@@ -2469,11 +2598,11 @@
         <v>78</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>157</v>
+        <v>112</v>
       </c>
       <c r="Y12" s="2"/>
       <c r="Z12" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>78</v>
@@ -2506,24 +2635,24 @@
         <v>100</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="AL12" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="AL12" t="s" s="2">
+      <c r="AM12" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="AM12" t="s" s="2">
+      <c r="AN12" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="AN12" t="s" s="2">
+    </row>
+    <row r="13" hidden="true">
+      <c r="A13" t="s" s="2">
         <v>162</v>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="2">
-        <v>163</v>
-      </c>
       <c r="B13" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2540,13 +2669,13 @@
         <v>78</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>108</v>
+        <v>163</v>
       </c>
       <c r="L13" t="s" s="2">
         <v>164</v>
@@ -2554,9 +2683,7 @@
       <c r="M13" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="N13" t="s" s="2">
-        <v>166</v>
-      </c>
+      <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>78</v>
@@ -2581,13 +2708,13 @@
         <v>78</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>167</v>
+        <v>78</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>168</v>
+        <v>78</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>169</v>
+        <v>78</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>78</v>
@@ -2605,7 +2732,7 @@
         <v>78</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>79</v>
@@ -2617,13 +2744,13 @@
         <v>78</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>78</v>
@@ -2632,23 +2759,23 @@
         <v>78</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>78</v>
@@ -2657,18 +2784,20 @@
         <v>78</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>172</v>
+        <v>134</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>173</v>
+        <v>135</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N14" s="2"/>
+        <v>169</v>
+      </c>
+      <c r="N14" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>78</v>
@@ -2705,51 +2834,51 @@
         <v>78</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>78</v>
+        <v>171</v>
       </c>
       <c r="AD14" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>78</v>
+        <v>172</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>175</v>
+        <v>78</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>177</v>
+        <v>78</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>178</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2760,30 +2889,32 @@
         <v>79</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="O15" s="2"/>
+        <v>178</v>
+      </c>
+      <c r="O15" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="P15" t="s" s="2">
         <v>78</v>
       </c>
@@ -2807,13 +2938,13 @@
         <v>78</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>183</v>
+        <v>78</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>184</v>
+        <v>78</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>185</v>
+        <v>78</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>78</v>
@@ -2831,13 +2962,13 @@
         <v>78</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>78</v>
@@ -2846,24 +2977,24 @@
         <v>100</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>186</v>
+        <v>78</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>188</v>
+        <v>182</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2877,7 +3008,7 @@
         <v>88</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>78</v>
@@ -2886,16 +3017,20 @@
         <v>89</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>190</v>
+        <v>163</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
+        <v>185</v>
+      </c>
+      <c r="N16" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="O16" t="s" s="2">
+        <v>187</v>
+      </c>
       <c r="P16" t="s" s="2">
         <v>78</v>
       </c>
@@ -2943,7 +3078,7 @@
         <v>78</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -2961,21 +3096,21 @@
         <v>78</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="17">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2986,28 +3121,28 @@
         <v>79</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>195</v>
+        <v>108</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3033,13 +3168,13 @@
         <v>78</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>78</v>
+        <v>195</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>78</v>
+        <v>196</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>78</v>
+        <v>197</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>78</v>
@@ -3057,13 +3192,13 @@
         <v>78</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>78</v>
@@ -3075,21 +3210,21 @@
         <v>78</v>
       </c>
       <c r="AL17" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AM17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN17" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="18" hidden="true">
+      <c r="A18" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="AM17" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s" s="2">
-        <v>200</v>
-      </c>
       <c r="B18" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3109,16 +3244,16 @@
         <v>78</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3169,7 +3304,7 @@
         <v>78</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -3181,41 +3316,41 @@
         <v>78</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="AL18" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="AM18" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="AM18" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="AN18" t="s" s="2">
-        <v>78</v>
+        <v>206</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>78</v>
@@ -3224,16 +3359,16 @@
         <v>78</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>134</v>
+        <v>153</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>135</v>
+        <v>208</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>137</v>
+        <v>210</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3259,13 +3394,13 @@
         <v>78</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>78</v>
+        <v>211</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>78</v>
+        <v>212</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>78</v>
+        <v>213</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>78</v>
@@ -3283,75 +3418,71 @@
         <v>78</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>78</v>
+        <v>214</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="20">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>210</v>
+        <v>78</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>134</v>
+        <v>163</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>211</v>
+        <v>164</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>78</v>
       </c>
@@ -3399,25 +3530,25 @@
         <v>78</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>213</v>
+        <v>166</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>131</v>
+        <v>167</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>78</v>
@@ -3426,23 +3557,23 @@
         <v>78</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>78</v>
@@ -3454,18 +3585,18 @@
         <v>78</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>215</v>
+        <v>134</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>216</v>
+        <v>135</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="N21" s="2"/>
-      <c r="O21" t="s" s="2">
-        <v>218</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>78</v>
       </c>
@@ -3501,51 +3632,51 @@
         <v>78</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>78</v>
+        <v>171</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>78</v>
+        <v>172</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>214</v>
+        <v>173</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>219</v>
+        <v>167</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>220</v>
+        <v>78</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3556,29 +3687,31 @@
         <v>79</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>222</v>
+        <v>175</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>223</v>
+        <v>176</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>177</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O22" t="s" s="2">
-        <v>225</v>
+        <v>179</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>78</v>
@@ -3627,13 +3760,13 @@
         <v>78</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>221</v>
+        <v>180</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>78</v>
@@ -3645,21 +3778,21 @@
         <v>78</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>226</v>
+        <v>181</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>78</v>
+        <v>182</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3673,25 +3806,29 @@
         <v>88</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>190</v>
+        <v>163</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>228</v>
+        <v>184</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
+        <v>185</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="O23" t="s" s="2">
+        <v>187</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>78</v>
       </c>
@@ -3739,7 +3876,7 @@
         <v>78</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>227</v>
+        <v>188</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -3754,24 +3891,24 @@
         <v>100</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>230</v>
+        <v>78</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="24">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3791,16 +3928,16 @@
         <v>78</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>195</v>
+        <v>222</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3851,7 +3988,7 @@
         <v>78</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -3866,10 +4003,10 @@
         <v>100</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>175</v>
+        <v>78</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>78</v>
@@ -3878,12 +4015,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3894,7 +4031,7 @@
         <v>79</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>78</v>
@@ -3906,15 +4043,17 @@
         <v>78</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>201</v>
+        <v>227</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>202</v>
+        <v>228</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N25" s="2"/>
+        <v>229</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>230</v>
+      </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>78</v>
@@ -3963,25 +4102,25 @@
         <v>78</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>204</v>
+        <v>226</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>205</v>
+        <v>231</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>78</v>
@@ -3990,23 +4129,23 @@
         <v>78</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>78</v>
@@ -4018,17 +4157,15 @@
         <v>78</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>134</v>
+        <v>163</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>78</v>
@@ -4077,25 +4214,25 @@
         <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>208</v>
+        <v>166</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>205</v>
+        <v>167</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>78</v>
@@ -4104,16 +4241,16 @@
         <v>78</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>210</v>
+        <v>133</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4126,26 +4263,24 @@
         <v>78</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K27" t="s" s="2">
         <v>134</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>211</v>
+        <v>135</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>212</v>
+        <v>169</v>
       </c>
       <c r="N27" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="O27" t="s" s="2">
-        <v>143</v>
-      </c>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>78</v>
       </c>
@@ -4193,7 +4328,7 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>213</v>
+        <v>173</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -4211,7 +4346,7 @@
         <v>78</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>131</v>
+        <v>167</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>78</v>
@@ -4220,44 +4355,48 @@
         <v>78</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>78</v>
+        <v>235</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>201</v>
+        <v>134</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N28" s="2"/>
-      <c r="O28" s="2"/>
+        <v>237</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>78</v>
       </c>
@@ -4305,39 +4444,39 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="AG28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AM28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN28" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="29" hidden="true">
+      <c r="A29" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="AG28" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH28" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI28" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ28" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK28" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="AL28" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s" s="2">
-        <v>243</v>
-      </c>
       <c r="B29" t="s" s="2">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4345,7 +4484,7 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>88</v>
@@ -4360,16 +4499,18 @@
         <v>78</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="N29" s="2"/>
-      <c r="O29" s="2"/>
+      <c r="O29" t="s" s="2">
+        <v>243</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>78</v>
       </c>
@@ -4405,22 +4546,20 @@
         <v>78</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="AC29" s="2"/>
       <c r="AD29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>78</v>
+        <v>172</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>88</v>
@@ -4432,19 +4571,1515 @@
         <v>100</v>
       </c>
       <c r="AK29" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="AM29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN29" t="s" s="2">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="C30" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="D30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E30" s="2"/>
+      <c r="F30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G30" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H30" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K30" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="P30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q30" s="2"/>
+      <c r="R30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF30" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AG30" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH30" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK30" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN30" t="s" s="2">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="31" hidden="true">
+      <c r="A31" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E31" s="2"/>
+      <c r="F31" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G31" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K31" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
+      <c r="P31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q31" s="2"/>
+      <c r="R31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF31" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AG31" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH31" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AM31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN31" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="32" hidden="true">
+      <c r="A32" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="C32" s="2"/>
+      <c r="D32" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="E32" s="2"/>
+      <c r="F32" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K32" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O32" s="2"/>
+      <c r="P32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q32" s="2"/>
+      <c r="R32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="AF32" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="AG32" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AM32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN32" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="C33" s="2"/>
+      <c r="D33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E33" s="2"/>
+      <c r="F33" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G33" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H33" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J33" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K33" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="AL29" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>248</v>
+      <c r="L33" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="P33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q33" s="2"/>
+      <c r="R33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF33" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="AG33" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH33" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="AM33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN33" t="s" s="2">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="C34" s="2"/>
+      <c r="D34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E34" s="2"/>
+      <c r="F34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G34" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H34" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J34" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K34" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="P34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q34" s="2"/>
+      <c r="R34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF34" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="AG34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH34" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN34" t="s" s="2">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="35" hidden="true">
+      <c r="A35" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E35" s="2"/>
+      <c r="F35" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G35" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K35" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="P35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q35" s="2"/>
+      <c r="R35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF35" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH35" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN35" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="36" hidden="true">
+      <c r="A36" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E36" s="2"/>
+      <c r="F36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G36" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K36" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M36" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
+      <c r="P36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q36" s="2"/>
+      <c r="R36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF36" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="AG36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH36" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK36" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN36" t="s" s="2">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="37" hidden="true">
+      <c r="A37" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E37" s="2"/>
+      <c r="F37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K37" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
+      <c r="P37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q37" s="2"/>
+      <c r="R37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF37" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK37" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN37" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="38" hidden="true">
+      <c r="A38" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E38" s="2"/>
+      <c r="F38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K38" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
+      <c r="P38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q38" s="2"/>
+      <c r="R38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF38" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN38" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="39" hidden="true">
+      <c r="A39" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="C39" s="2"/>
+      <c r="D39" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="E39" s="2"/>
+      <c r="F39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K39" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O39" s="2"/>
+      <c r="P39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q39" s="2"/>
+      <c r="R39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF39" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="AG39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN39" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="40" hidden="true">
+      <c r="A40" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="C40" s="2"/>
+      <c r="D40" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="E40" s="2"/>
+      <c r="F40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I40" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="J40" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K40" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="P40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q40" s="2"/>
+      <c r="R40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF40" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN40" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="41" hidden="true">
+      <c r="A41" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="C41" s="2"/>
+      <c r="D41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E41" s="2"/>
+      <c r="F41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G41" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K41" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
+      <c r="P41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q41" s="2"/>
+      <c r="R41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF41" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH41" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK41" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN41" t="s" s="2">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="42" hidden="true">
+      <c r="A42" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E42" s="2"/>
+      <c r="F42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K42" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
+      <c r="P42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q42" s="2"/>
+      <c r="R42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF42" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AG42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH42" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK42" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN42" t="s" s="2">
+        <v>284</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AN42">
+    <filterColumn colId="7">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="27">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI41">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/dev/StructureDefinition-ph-core-medication.xlsx
+++ b/dev/StructureDefinition-ph-core-medication.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T05:32:03+00:00</t>
+    <t>2026-04-10T05:44:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-medication.xlsx
+++ b/dev/StructureDefinition-ph-core-medication.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T05:44:36+00:00</t>
+    <t>2026-05-26T03:51:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-medication.xlsx
+++ b/dev/StructureDefinition-ph-core-medication.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T03:51:01+00:00</t>
+    <t>2026-05-26T04:00:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-medication.xlsx
+++ b/dev/StructureDefinition-ph-core-medication.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T04:00:40+00:00</t>
+    <t>2026-05-26T04:36:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
